--- a/BWI/bestwine_output/bestwine_Panama.xlsx
+++ b/BWI/bestwine_output/bestwine_Panama.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA71"/>
+  <dimension ref="A1:AA72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -8095,6 +8095,79 @@
         </is>
       </c>
     </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>Enowines 507, S.a.</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>Enowines 507, S.a.</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>108449</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>Panama</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>Panamá</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>Provincia de Panamá</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>Av Israel , Plaza Sunsei Strip , Pb, Local 011 Al Lado De Las Capillas</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr"/>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>https://enowines507.com</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr"/>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr"/>
+      <c r="M72" s="2" t="inlineStr"/>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>contacto@enowines507.com</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr"/>
+      <c r="P72" s="2" t="inlineStr"/>
+      <c r="Q72" s="2" t="inlineStr"/>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr"/>
+      <c r="V72" s="2" t="inlineStr"/>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>Maxiel Figueroa</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>Sommelier</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr"/>
+      <c r="Z72" s="2" t="inlineStr"/>
+      <c r="AA72" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Panama.xlsx
+++ b/BWI/bestwine_output/bestwine_Panama.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA72"/>
+  <dimension ref="A1:AA73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -8168,6 +8168,79 @@
       <c r="Z72" s="2" t="inlineStr"/>
       <c r="AA72" s="2" t="inlineStr"/>
     </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>Enowines 507, S.a.</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>Enowines 507, S.a.</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>108449</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>Panama</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>Panamá</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>Provincia de Panamá</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>Av Israel , Plaza Sunsei Strip , Pb, Local 011 Al Lado De Las Capillas</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr"/>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>https://enowines507.com</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr"/>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr"/>
+      <c r="M73" s="2" t="inlineStr"/>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>contacto@enowines507.com</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr"/>
+      <c r="P73" s="2" t="inlineStr"/>
+      <c r="Q73" s="2" t="inlineStr"/>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr"/>
+      <c r="V73" s="2" t="inlineStr"/>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>Maxiel Figueroa</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>Sommelier</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr"/>
+      <c r="Z73" s="2" t="inlineStr"/>
+      <c r="AA73" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Panama.xlsx
+++ b/BWI/bestwine_output/bestwine_Panama.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA73"/>
+  <dimension ref="A1:AA75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -8241,6 +8241,176 @@
       <c r="Z73" s="2" t="inlineStr"/>
       <c r="AA73" s="2" t="inlineStr"/>
     </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>Ueta Latinoamerica Inc.</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>Ueta Latinoamerica Inc.</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>45598</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>Panama</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>Panamá</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>Panamá</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>Santa Maria Business District</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr"/>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>https://uetainc.com</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr"/>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr"/>
+      <c r="M74" s="2" t="inlineStr"/>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>info@uetainc.com</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>+507 430-7770</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr"/>
+      <c r="Q74" s="2" t="inlineStr"/>
+      <c r="R74" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/ueta-inc./</t>
+        </is>
+      </c>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr"/>
+      <c r="V74" s="2" t="inlineStr"/>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>Eduardo F.</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>Food and Beverage Manager</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr"/>
+      <c r="Z74" s="2" t="inlineStr"/>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/eduardo-f-57415b107/</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>Ueta Latinoamerica Inc.</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>Ueta Latinoamerica Inc.</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>45598</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>Panama</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>Panamá</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>Panamá</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>Santa Maria Business District</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr"/>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>https://uetainc.com</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr"/>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr"/>
+      <c r="M75" s="2" t="inlineStr"/>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>info@uetainc.com</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>+507 430-7770</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr"/>
+      <c r="Q75" s="2" t="inlineStr"/>
+      <c r="R75" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/ueta-inc./</t>
+        </is>
+      </c>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr"/>
+      <c r="V75" s="2" t="inlineStr"/>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>Graciela De la Garza</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>Management Assistant</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr"/>
+      <c r="Z75" s="2" t="inlineStr"/>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/graciela-de-la-garza-184b2144/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Panama.xlsx
+++ b/BWI/bestwine_output/bestwine_Panama.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA75"/>
+  <dimension ref="A1:AA79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -8411,6 +8411,394 @@
         </is>
       </c>
     </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>Top Brands International, S.a</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>Top Brands International, S.a</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>22096</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>Panama</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>Panamá</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>Provincia de Panamá</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>Punta Pacífica Edif. Grand Plaza, Piso #8</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr"/>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>https://topbrandsint.com</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr"/>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr"/>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>contactenos@topbrandsint.com</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>+507 265-1655</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>1997</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr">
+        <is>
+          <t>563252335841</t>
+        </is>
+      </c>
+      <c r="R76" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/topbrandsint./</t>
+        </is>
+      </c>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr"/>
+      <c r="V76" s="2" t="inlineStr"/>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>Esther Melany Esquivel Solís</t>
+        </is>
+      </c>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>Purchasing Analyst</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr"/>
+      <c r="Z76" s="2" t="inlineStr"/>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/esther-melany-esquivel-sol%C3%ADs-84958315b/</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>Top Brands International, S.a</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>Top Brands International, S.a</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>22096</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>Panama</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>Panamá</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>Provincia de Panamá</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>Punta Pacífica Edif. Grand Plaza, Piso #8</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr"/>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>https://topbrandsint.com</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr"/>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr"/>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>contactenos@topbrandsint.com</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>+507 265-1655</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>1997</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr">
+        <is>
+          <t>563252335841</t>
+        </is>
+      </c>
+      <c r="R77" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/topbrandsint./</t>
+        </is>
+      </c>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr"/>
+      <c r="V77" s="2" t="inlineStr"/>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>Danny Yohoros</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>President</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr"/>
+      <c r="Z77" s="2" t="inlineStr"/>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/danny-yohoros-76027b146/</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>El Machetazo, S.a.</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>El Machetazo, S.a.</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>69530</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>Panama</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>Panamá</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>Provincia de Panamá</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>Avenida Republica del Perú</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr"/>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>https://www.elmachetazo.com</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr"/>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr"/>
+      <c r="M78" s="2" t="inlineStr"/>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>info@machetazo.com</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>+507 207-0200</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr"/>
+      <c r="Q78" s="2" t="inlineStr"/>
+      <c r="R78" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/grupo-el-machetazo/</t>
+        </is>
+      </c>
+      <c r="S78" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/elmachetazofans</t>
+        </is>
+      </c>
+      <c r="T78" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/machetazopanama/</t>
+        </is>
+      </c>
+      <c r="U78" s="2" t="inlineStr"/>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@elmachetazopanama</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>Ronald Maschkowski</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Commercial Operations Manager </t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr"/>
+      <c r="Z78" s="2" t="inlineStr"/>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ronald-maschkowski-037216161/</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>El Machetazo, S.a.</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>El Machetazo, S.a.</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>69530</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>Panama</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>Panamá</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>Provincia de Panamá</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>Avenida Republica del Perú</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr"/>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>https://www.elmachetazo.com</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr"/>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr"/>
+      <c r="M79" s="2" t="inlineStr"/>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>info@machetazo.com</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>+507 207-0200</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr"/>
+      <c r="Q79" s="2" t="inlineStr"/>
+      <c r="R79" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/grupo-el-machetazo/</t>
+        </is>
+      </c>
+      <c r="S79" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/elmachetazofans</t>
+        </is>
+      </c>
+      <c r="T79" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/machetazopanama/</t>
+        </is>
+      </c>
+      <c r="U79" s="2" t="inlineStr"/>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@elmachetazopanama</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>Mario Effio</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>Sales Director</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr"/>
+      <c r="Z79" s="2" t="inlineStr"/>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/mario-effio-311bb168/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
